--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -199,7 +199,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'UkNmg DryrunTesting' Employee:{10698967}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+    <t xml:space="preserve">Test failed for 'Torrance Goyette' Employee:{10698973}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
 Expected: [32m"UK Staff Group 30"[39m
 Received: [31m"UK Staff Group 30[7m_Test[27m"[39m</t>
   </si>
@@ -216,10 +216,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>UkNmg</t>
-  </si>
-  <si>
-    <t>DryrunTesting</t>
+    <t>Torrance</t>
+  </si>
+  <si>
+    <t>Goyette</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -300,7 +300,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911913A</t>
+    <t>AB911915A</t>
   </si>
   <si>
     <t>Male</t>
@@ -327,22 +327,28 @@
     <t>Checking</t>
   </si>
   <si>
-    <t>UK Staff Group 30</t>
+    <t>UK Staff Group 30_Test</t>
   </si>
   <si>
     <t>Test2</t>
   </si>
   <si>
-    <t>Test failed for 'UkMg DryrunTesting' Employee:{10698968}TypeError: Cannot read properties of undefined (reading 'match')</t>
+    <t xml:space="preserve">Test failed for 'Jerod Nicolas-McDermott' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
+</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>UkMg</t>
-  </si>
-  <si>
-    <t>Auto 18071762</t>
+    <t>Jerod</t>
+  </si>
+  <si>
+    <t>Nicolas-McDermott</t>
+  </si>
+  <si>
+    <t>Auto 5317457</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -354,7 +360,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911914A</t>
+    <t>AB911916A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -1397,7 +1403,7 @@
         <v>106</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>67</v>
@@ -1456,13 +1462,13 @@
         <v>78</v>
       </c>
       <c r="AA3" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AB3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC3" s="23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD3" s="24" t="s">
         <v>82</v>
@@ -1492,10 +1498,10 @@
         <v>87</v>
       </c>
       <c r="AM3" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO3" s="7" t="s">
         <v>91</v>
@@ -1513,7 +1519,7 @@
         <v>92</v>
       </c>
       <c r="AT3" s="30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AU3" s="7" t="s">
         <v>94</v>
@@ -1558,7 +1564,7 @@
         <v>101</v>
       </c>
       <c r="BI3" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="2:61" s="7" customFormat="1" x14ac:dyDescent="0.25">

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -298,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB920886A</t>
+    <t>AB922886A</t>
   </si>
   <si>
     <t>Male</t>
@@ -331,19 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698958</t>
+    <t>10698971</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Maxwell</t>
-  </si>
-  <si>
-    <t>Harvey</t>
-  </si>
-  <si>
-    <t>Auto 39339321</t>
+    <t>Donato</t>
+  </si>
+  <si>
+    <t>Kutch</t>
+  </si>
+  <si>
+    <t>Auto 24043355</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB920887A</t>
+    <t>AB922887A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-30</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="X2" s="16">
         <f>TODAY()-30</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="L3" s="16">
         <f>TODAY()-30</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="X3" s="16">
         <f>TODAY()-30</f>
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="0"/>
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F431E17A-194C-4BD6-8D66-B69C8D254CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BI$3</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="111">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -199,12 +213,6 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698957</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>519 Recruitment (Fozac Hosoti (9575064) (Inherited))</t>
   </si>
   <si>
@@ -329,9 +337,6 @@
   </si>
   <si>
     <t>Test2</t>
-  </si>
-  <si>
-    <t>10698971</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
@@ -364,78 +369,78 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF040C28"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="10"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Calibri Light"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
   </fonts>
   <fills count="6">
@@ -447,7 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +469,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,15 +489,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -878,10 +895,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
@@ -940,10 +957,11 @@
     <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
     <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
-    <col min="62" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="62" max="62" width="8.90625" style="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1131,105 +1149,101 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="F2" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="H2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="I2" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="L2" s="16">
+        <f ca="1">TODAY()-30</f>
+        <v>45762</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="O2" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="16">
-        <f>TODAY()-30</f>
-        <v>45755</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N2" s="17" t="s">
+      <c r="P2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="Q2" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="R2" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="S2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="T2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="V2" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="T2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="U2" s="19" t="s">
+      <c r="W2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" s="16">
+        <f ca="1">TODAY()-30</f>
+        <v>45762</v>
+      </c>
+      <c r="Y2" s="19">
+        <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
+        <v>45852</v>
+      </c>
+      <c r="Z2" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="AA2" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="W2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="X2" s="16">
-        <f>TODAY()-30</f>
-        <v>45755</v>
-      </c>
-      <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45845</v>
-      </c>
-      <c r="Z2" s="15" t="s">
+      <c r="AB2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AC2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AD2" s="23" t="s">
         <v>80</v>
-      </c>
-      <c r="AC2" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD2" s="23" t="s">
-        <v>82</v>
       </c>
       <c r="AE2" s="24">
         <v>519</v>
       </c>
       <c r="AF2" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AG2" s="25">
         <v>37.5</v>
@@ -1238,73 +1252,73 @@
         <v>37.5</v>
       </c>
       <c r="AI2" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AL2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="AK2" s="27" t="s">
+      <c r="AM2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="AL2" s="15" t="s">
+      <c r="AN2" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AM2" s="15" t="s">
+      <c r="AO2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AP2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AR2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS2" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="AP2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AT2" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AR2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS2" s="28" t="s">
+      <c r="AU2" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="AT2" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="AU2" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV2" s="30">
         <v>35591</v>
       </c>
       <c r="AW2" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY2" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ2" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA2" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY2" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BB2" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="BA2" s="30" t="s">
+      <c r="BC2" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="BB2" s="30" t="s">
+      <c r="BD2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE2" s="28" t="s">
         <v>98</v>
-      </c>
-      <c r="BC2" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD2" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE2" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF2" s="15">
         <v>601613</v>
@@ -1313,105 +1327,101 @@
         <v>31926819</v>
       </c>
       <c r="BH2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="BI2" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="BI2" s="15" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="E3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="I3" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="16">
+        <f ca="1">TODAY()-30</f>
+        <v>45762</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="N3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="16">
+        <f ca="1">TODAY()-30</f>
+        <v>45762</v>
+      </c>
+      <c r="Y3" s="19">
+        <f t="shared" ca="1" si="0"/>
+        <v>45852</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA3" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="13" t="s">
+      <c r="AB3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC3" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" s="16">
-        <f>TODAY()-30</f>
-        <v>45755</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="V3" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="X3" s="16">
-        <f>TODAY()-30</f>
-        <v>45755</v>
-      </c>
-      <c r="Y3" s="19">
-        <f t="shared" si="0"/>
-        <v>45845</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AD3" s="23" t="s">
         <v>80</v>
-      </c>
-      <c r="AC3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD3" s="23" t="s">
-        <v>82</v>
       </c>
       <c r="AE3" s="24">
         <v>519</v>
@@ -1426,73 +1436,73 @@
         <v>40</v>
       </c>
       <c r="AI3" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ3" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK3" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" s="23" t="s">
+      <c r="AL3" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="AK3" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL3" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="AM3" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AP3" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AQ3" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AS3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AT3" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="AU3" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="AT3" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="AU3" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="AV3" s="30">
         <v>35591</v>
       </c>
       <c r="AW3" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AX3" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AY3" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="AZ3" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BA3" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AY3" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="BB3" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="BA3" s="30" t="s">
+      <c r="BC3" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="BB3" s="30" t="s">
+      <c r="BD3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE3" s="28" t="s">
         <v>98</v>
-      </c>
-      <c r="BC3" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD3" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE3" s="28" t="s">
-        <v>100</v>
       </c>
       <c r="BF3" s="15">
         <v>601613</v>
@@ -1501,37 +1511,25 @@
         <v>31926819</v>
       </c>
       <c r="BH3" s="28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="BI3" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 Z2:Z3 W2:W3 T2:T3 K2:K3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="AI2" r:id="rId2"/>
-    <hyperlink ref="V3" r:id="rId3"/>
-    <hyperlink ref="AI3" r:id="rId4"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AI2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F431E17A-194C-4BD6-8D66-B69C8D254CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BI$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="114">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,6 +199,12 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>10699104</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>519 Recruitment (Fozac Hosoti (9575064) (Inherited))</t>
   </si>
   <si>
@@ -222,10 +214,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Elias</t>
-  </si>
-  <si>
-    <t>Hand</t>
+    <t>Clementine</t>
+  </si>
+  <si>
+    <t>Dare</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -306,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB922886A</t>
+    <t>AB922888A</t>
   </si>
   <si>
     <t>Male</t>
@@ -339,16 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10699105</t>
+  </si>
+  <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Donato</t>
-  </si>
-  <si>
-    <t>Kutch</t>
-  </si>
-  <si>
-    <t>Auto 24043355</t>
+    <t>Therese</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>Auto 23058354</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -360,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB922887A</t>
+    <t>AB922889A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -369,78 +364,78 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF040C28"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color theme="10"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="major"/>
       <sz val="10"/>
       <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="6">
@@ -452,7 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,27 +484,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -895,10 +878,10 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
@@ -957,11 +940,10 @@
     <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
     <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="8.90625" style="1" customWidth="1"/>
-    <col min="63" max="16384" width="8.90625" style="1"/>
+    <col min="62" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.5" customHeight="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1149,101 +1131,105 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
+      <c r="B2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="D2" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="16">
+        <f>TODAY()-30</f>
+        <v>45763</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45762</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>61</v>
-      </c>
       <c r="N2" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="R2" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="T2" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="U2" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X2" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45762</v>
+        <f>TODAY()-30</f>
+        <v>45763</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
-        <v>45852</v>
+        <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
+        <v>45853</v>
       </c>
       <c r="Z2" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC2" s="22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AE2" s="24">
         <v>519</v>
       </c>
       <c r="AF2" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG2" s="25">
         <v>37.5</v>
@@ -1252,73 +1238,73 @@
         <v>37.5</v>
       </c>
       <c r="AI2" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AJ2" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK2" s="27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL2" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AM2" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AQ2" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AR2" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AS2" s="28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AT2" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AU2" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AV2" s="30">
         <v>35591</v>
       </c>
       <c r="AW2" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AX2" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AY2" s="30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AZ2" s="30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BA2" s="30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BC2" s="31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BD2" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="BE2" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BF2" s="15">
         <v>601613</v>
@@ -1327,101 +1313,105 @@
         <v>31926819</v>
       </c>
       <c r="BH2" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BI2" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
+        <v>103</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="D3" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L3" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45762</v>
+        <f>TODAY()-30</f>
+        <v>45763</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O3" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="U3" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V3" s="20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X3" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45762</v>
+        <f>TODAY()-30</f>
+        <v>45763</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>45852</v>
+        <f t="shared" si="0"/>
+        <v>45853</v>
       </c>
       <c r="Z3" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AE3" s="24">
         <v>519</v>
@@ -1436,73 +1426,73 @@
         <v>40</v>
       </c>
       <c r="AI3" s="26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AJ3" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AK3" s="27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AL3" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AM3" s="15" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AP3" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AQ3" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AS3" s="28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AT3" s="29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AU3" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AV3" s="30">
         <v>35591</v>
       </c>
       <c r="AW3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AY3" s="30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AZ3" s="30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BA3" s="30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BC3" s="31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BD3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="BE3" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BF3" s="15">
         <v>601613</v>
@@ -1511,25 +1501,37 @@
         <v>31926819</v>
       </c>
       <c r="BH3" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BI3" s="15" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 Z2:Z3 W2:W3 T2:T3 K2:K3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AI2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="V3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="AI2" r:id="rId2"/>
+    <hyperlink ref="V3" r:id="rId3"/>
+    <hyperlink ref="AI3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -199,7 +199,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698957</t>
+    <t>10699404</t>
   </si>
   <si>
     <t>Passed</t>
@@ -214,10 +214,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Elias</t>
-  </si>
-  <si>
-    <t>Hand</t>
+    <t>Lane</t>
+  </si>
+  <si>
+    <t>Cummings</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -298,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB922886A</t>
+    <t>AB922890A</t>
   </si>
   <si>
     <t>Male</t>
@@ -331,19 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698971</t>
+    <t>10699431</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Donato</t>
-  </si>
-  <si>
-    <t>Kutch</t>
-  </si>
-  <si>
-    <t>Auto 24043355</t>
+    <t>Annamae</t>
+  </si>
+  <si>
+    <t>Stanton</t>
+  </si>
+  <si>
+    <t>Auto 1901633</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB922887A</t>
+    <t>AB922902A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -884,7 +884,7 @@
   <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.90625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
@@ -940,7 +940,8 @@
     <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
     <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
     <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
-    <col min="62" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="62" max="62" width="21.6328125" style="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1167,7 +1168,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-30</f>
-        <v>45755</v>
+        <v>45775</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1204,11 +1205,11 @@
       </c>
       <c r="X2" s="16">
         <f>TODAY()-30</f>
-        <v>45755</v>
+        <v>45775</v>
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45845</v>
+        <v>45865</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1355,7 +1356,7 @@
       </c>
       <c r="L3" s="16">
         <f>TODAY()-30</f>
-        <v>45755</v>
+        <v>45775</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1392,11 +1393,11 @@
       </c>
       <c r="X3" s="16">
         <f>TODAY()-30</f>
-        <v>45755</v>
+        <v>45775</v>
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="0"/>
-        <v>45845</v>
+        <v>45865</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -199,7 +199,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699104</t>
+    <t>10699545</t>
   </si>
   <si>
     <t>Passed</t>
@@ -214,10 +214,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Clementine</t>
-  </si>
-  <si>
-    <t>Dare</t>
+    <t>Dariana</t>
+  </si>
+  <si>
+    <t>Mills</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -298,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB922888A</t>
+    <t>AB922991A</t>
   </si>
   <si>
     <t>Male</t>
@@ -331,19 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699105</t>
+    <t>10699546</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Therese</t>
-  </si>
-  <si>
-    <t>Jenkins</t>
-  </si>
-  <si>
-    <t>Auto 23058354</t>
+    <t>Austyn</t>
+  </si>
+  <si>
+    <t>Kessler</t>
+  </si>
+  <si>
+    <t>Auto 22597601</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB922889A</t>
+    <t>AB922992A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-30</f>
-        <v>45763</v>
+        <v>45780</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="X2" s="16">
         <f>TODAY()-30</f>
-        <v>45763</v>
+        <v>45780</v>
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45853</v>
+        <v>45870</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="L3" s="16">
         <f>TODAY()-30</f>
-        <v>45763</v>
+        <v>45780</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="X3" s="16">
         <f>TODAY()-30</f>
-        <v>45763</v>
+        <v>45780</v>
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="0"/>
-        <v>45853</v>
+        <v>45870</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -1,18 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20F27DB-B04B-4255-8A24-D171BAE5A8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BI$3</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -199,7 +213,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698957</t>
+    <t>10698984</t>
   </si>
   <si>
     <t>Passed</t>
@@ -214,10 +228,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Elias</t>
-  </si>
-  <si>
-    <t>Hand</t>
+    <t>Zander</t>
+  </si>
+  <si>
+    <t>Jacobi</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -298,7 +312,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB920886A</t>
+    <t>AB911924A</t>
   </si>
   <si>
     <t>Male</t>
@@ -331,19 +345,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698958</t>
+    <t>10698986</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Maxwell</t>
-  </si>
-  <si>
-    <t>Harvey</t>
-  </si>
-  <si>
-    <t>Auto 39339321</t>
+    <t>Nichole</t>
+  </si>
+  <si>
+    <t>Connelly</t>
+  </si>
+  <si>
+    <t>Auto 58816246</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -355,7 +369,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB920887A</t>
+    <t>AB911925A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -364,78 +378,78 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF040C28"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color theme="10"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4A4A4A"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Calibri Light"/>
-    </font>
-    <font>
-      <color rgb="FF4A4A4A"/>
       <family val="2"/>
       <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="major"/>
-      <sz val="10"/>
-      <name val="Calibri Light"/>
     </font>
   </fonts>
   <fills count="6">
@@ -447,7 +461,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +478,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,15 +498,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -878,72 +904,73 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.36328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.453125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.08984375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.81640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.453125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" style="1" customWidth="1"/>
-    <col min="18" max="19" width="11.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.08984375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.1796875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.36328125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="1" customWidth="1"/>
+    <col min="18" max="19" width="11.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.109375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.21875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13.77734375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="17.33203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.77734375" style="1" customWidth="1"/>
     <col min="27" max="27" width="26" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.36328125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.33203125" style="1" customWidth="1"/>
     <col min="29" max="29" width="15" style="1" customWidth="1"/>
     <col min="30" max="30" width="10" style="1" customWidth="1"/>
-    <col min="31" max="31" width="8.6328125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.6328125" style="1" customWidth="1"/>
-    <col min="33" max="34" width="22.453125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="27.08984375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
+    <col min="33" max="34" width="22.44140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="27.109375" style="1" customWidth="1"/>
     <col min="36" max="36" width="10" style="1" customWidth="1"/>
-    <col min="37" max="37" width="19.6328125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="28.36328125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="21.54296875" style="1" customWidth="1"/>
-    <col min="40" max="40" width="22.6328125" style="1" customWidth="1"/>
-    <col min="41" max="42" width="53.6328125" style="1" customWidth="1"/>
-    <col min="43" max="43" width="9.54296875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.453125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="29.90625" style="1" customWidth="1"/>
-    <col min="46" max="46" width="12.1796875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="7.453125" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.81640625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.453125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="19.6640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="28.33203125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="21.5546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6640625" style="1" customWidth="1"/>
+    <col min="41" max="42" width="53.6640625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9.5546875" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15.44140625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="29.88671875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="12.21875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="7.44140625" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.77734375" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.44140625" style="1" customWidth="1"/>
     <col min="50" max="50" width="14" style="1" customWidth="1"/>
-    <col min="51" max="51" width="11.36328125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="11.33203125" style="1" customWidth="1"/>
     <col min="52" max="52" width="25" style="1" customWidth="1"/>
     <col min="53" max="53" width="17" style="1" customWidth="1"/>
-    <col min="54" max="54" width="30.08984375" style="1" customWidth="1"/>
-    <col min="55" max="55" width="9.6328125" style="1" customWidth="1"/>
+    <col min="54" max="54" width="30.109375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9.6640625" style="1" customWidth="1"/>
     <col min="56" max="56" width="18" style="1" customWidth="1"/>
-    <col min="57" max="58" width="13.90625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
-    <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
-    <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
-    <col min="62" max="16384" width="8.90625" style="1" customWidth="1"/>
+    <col min="57" max="58" width="13.88671875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15.33203125" style="1" customWidth="1"/>
+    <col min="60" max="60" width="12.6640625" style="1" customWidth="1"/>
+    <col min="61" max="61" width="26.21875" style="1" customWidth="1"/>
+    <col min="62" max="62" width="8.88671875" style="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1158,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
@@ -1166,8 +1193,8 @@
         <v>69</v>
       </c>
       <c r="L2" s="16">
-        <f>TODAY()-30</f>
-        <v>45754</v>
+        <f ca="1">TODAY()-30</f>
+        <v>45756</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1203,12 +1230,12 @@
         <v>69</v>
       </c>
       <c r="X2" s="16">
-        <f>TODAY()-30</f>
-        <v>45754</v>
+        <f ca="1">TODAY()-30</f>
+        <v>45756</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45844</v>
+        <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
+        <v>45846</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1319,7 +1346,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
@@ -1354,8 +1381,8 @@
         <v>69</v>
       </c>
       <c r="L3" s="16">
-        <f>TODAY()-30</f>
-        <v>45754</v>
+        <f ca="1">TODAY()-30</f>
+        <v>45756</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1391,12 +1418,12 @@
         <v>69</v>
       </c>
       <c r="X3" s="16">
-        <f>TODAY()-30</f>
-        <v>45754</v>
+        <f ca="1">TODAY()-30</f>
+        <v>45756</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" si="0"/>
-        <v>45844</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45846</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>
@@ -1508,30 +1535,18 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 Z2:Z3 W2:W3 T2:T3 K2:K3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="AI2" r:id="rId2"/>
-    <hyperlink ref="V3" r:id="rId3"/>
-    <hyperlink ref="AI3" r:id="rId4"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AI2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -199,7 +199,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10699545</t>
+    <t>10699627</t>
   </si>
   <si>
     <t>Passed</t>
@@ -214,10 +214,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Dariana</t>
-  </si>
-  <si>
-    <t>Mills</t>
+    <t>Floy</t>
+  </si>
+  <si>
+    <t>Rohan</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -298,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB922991A</t>
+    <t>AB922993A</t>
   </si>
   <si>
     <t>Male</t>
@@ -331,19 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10699546</t>
+    <t>10699629</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Austyn</t>
-  </si>
-  <si>
-    <t>Kessler</t>
-  </si>
-  <si>
-    <t>Auto 22597601</t>
+    <t>Danika</t>
+  </si>
+  <si>
+    <t>Satterfield</t>
+  </si>
+  <si>
+    <t>Auto 19353761</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB922992A</t>
+    <t>AB922994A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-30</f>
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="X2" s="16">
         <f>TODAY()-30</f>
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="Y2" s="19">
         <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
-        <v>45870</v>
+        <v>45877</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="L3" s="16">
         <f>TODAY()-30</f>
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1392,11 +1392,11 @@
       </c>
       <c r="X3" s="16">
         <f>TODAY()-30</f>
-        <v>45780</v>
+        <v>45787</v>
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="0"/>
-        <v>45870</v>
+        <v>45877</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -1,32 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20F27DB-B04B-4255-8A24-D171BAE5A8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet sheetId="2" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BI$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -213,7 +199,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10698984</t>
+    <t>10699762</t>
   </si>
   <si>
     <t>Passed</t>
@@ -228,10 +214,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Zander</t>
-  </si>
-  <si>
-    <t>Jacobi</t>
+    <t>Floy</t>
+  </si>
+  <si>
+    <t>Rohan</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -312,7 +298,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911924A</t>
+    <t>AB922995A</t>
   </si>
   <si>
     <t>Male</t>
@@ -345,19 +331,19 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10698986</t>
+    <t>10699763</t>
   </si>
   <si>
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Nichole</t>
-  </si>
-  <si>
-    <t>Connelly</t>
-  </si>
-  <si>
-    <t>Auto 58816246</t>
+    <t>Danika</t>
+  </si>
+  <si>
+    <t>Satterfield</t>
+  </si>
+  <si>
+    <t>Auto 94349662</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -369,7 +355,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911925A</t>
+    <t>AB922996A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -378,78 +364,78 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="1"/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF040C28"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
       <color theme="10"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="major"/>
       <sz val="10"/>
       <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="6">
@@ -461,7 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,27 +484,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -904,73 +878,72 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.90625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.77734375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.44140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" style="1" customWidth="1"/>
-    <col min="18" max="19" width="11.109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.21875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13.77734375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.33203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.1796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.08984375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.81640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.453125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" style="1" customWidth="1"/>
+    <col min="18" max="19" width="11.08984375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.1796875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13.81640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="17.36328125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.81640625" style="1" customWidth="1"/>
     <col min="27" max="27" width="26" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.36328125" style="1" customWidth="1"/>
     <col min="29" max="29" width="15" style="1" customWidth="1"/>
     <col min="30" max="30" width="10" style="1" customWidth="1"/>
-    <col min="31" max="31" width="8.6640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
-    <col min="33" max="34" width="22.44140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="27.109375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6328125" style="1" customWidth="1"/>
+    <col min="33" max="34" width="22.453125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="27.08984375" style="1" customWidth="1"/>
     <col min="36" max="36" width="10" style="1" customWidth="1"/>
-    <col min="37" max="37" width="19.6640625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="28.33203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="21.5546875" style="1" customWidth="1"/>
-    <col min="40" max="40" width="22.6640625" style="1" customWidth="1"/>
-    <col min="41" max="42" width="53.6640625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="9.5546875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.44140625" style="1" customWidth="1"/>
-    <col min="45" max="45" width="29.88671875" style="1" customWidth="1"/>
-    <col min="46" max="46" width="12.21875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="7.44140625" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.77734375" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.44140625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="19.6328125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="28.36328125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="21.54296875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6328125" style="1" customWidth="1"/>
+    <col min="41" max="42" width="53.6328125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9.54296875" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15.453125" style="1" customWidth="1"/>
+    <col min="45" max="45" width="29.90625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="12.1796875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="7.453125" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.81640625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.453125" style="1" customWidth="1"/>
     <col min="50" max="50" width="14" style="1" customWidth="1"/>
-    <col min="51" max="51" width="11.33203125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="11.36328125" style="1" customWidth="1"/>
     <col min="52" max="52" width="25" style="1" customWidth="1"/>
     <col min="53" max="53" width="17" style="1" customWidth="1"/>
-    <col min="54" max="54" width="30.109375" style="1" customWidth="1"/>
-    <col min="55" max="55" width="9.6640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="30.08984375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9.6328125" style="1" customWidth="1"/>
     <col min="56" max="56" width="18" style="1" customWidth="1"/>
-    <col min="57" max="58" width="13.88671875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15.33203125" style="1" customWidth="1"/>
-    <col min="60" max="60" width="12.6640625" style="1" customWidth="1"/>
-    <col min="61" max="61" width="26.21875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="8.88671875" style="1" customWidth="1"/>
-    <col min="63" max="16384" width="8.88671875" style="1"/>
+    <col min="57" max="58" width="13.90625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
+    <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
+    <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
+    <col min="62" max="16384" width="8.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.5" customHeight="1" spans="1:62" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1131,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
@@ -1193,8 +1166,8 @@
         <v>69</v>
       </c>
       <c r="L2" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45756</v>
+        <f>TODAY()-30</f>
+        <v>45796</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>63</v>
@@ -1230,12 +1203,12 @@
         <v>69</v>
       </c>
       <c r="X2" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45756</v>
+        <f>TODAY()-30</f>
+        <v>45796</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
-        <v>45846</v>
+        <f t="shared" ref="Y2:Y3" si="0">X2+90</f>
+        <v>45886</v>
       </c>
       <c r="Z2" s="15" t="s">
         <v>78</v>
@@ -1346,7 +1319,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:62" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="15" customHeight="1" spans="1:61" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
@@ -1381,8 +1354,8 @@
         <v>69</v>
       </c>
       <c r="L3" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45756</v>
+        <f>TODAY()-30</f>
+        <v>45796</v>
       </c>
       <c r="M3" s="11" t="s">
         <v>63</v>
@@ -1418,12 +1391,12 @@
         <v>69</v>
       </c>
       <c r="X3" s="16">
-        <f ca="1">TODAY()-30</f>
-        <v>45756</v>
+        <f>TODAY()-30</f>
+        <v>45796</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>45846</v>
+        <f t="shared" si="0"/>
+        <v>45886</v>
       </c>
       <c r="Z3" s="15" t="s">
         <v>78</v>
@@ -1535,18 +1508,30 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3 Z2:Z3 W2:W3 T2:T3 K2:K3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AI2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="V3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="AI2" r:id="rId2"/>
+    <hyperlink ref="V3" r:id="rId3"/>
+    <hyperlink ref="AI3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E2A09A-6949-4C5B-ACC6-273ADCBD0AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C866912A-3A72-4E44-B045-FBEED9231E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,10 +222,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Ila</t>
-  </si>
-  <si>
-    <t>Dickens</t>
+    <t>Barry</t>
+  </si>
+  <si>
+    <t>Runolfsson</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -306,7 +306,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB923135A</t>
+    <t>AB923148A</t>
   </si>
   <si>
     <t>Male</t>
@@ -342,13 +342,13 @@
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Griffin</t>
-  </si>
-  <si>
-    <t>Grant</t>
-  </si>
-  <si>
-    <t>Auto 67794496</t>
+    <t>Wilber</t>
+  </si>
+  <si>
+    <t>Kuvalis</t>
+  </si>
+  <si>
+    <t>Auto 30608985</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -360,7 +360,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB923136A</t>
+    <t>AB923149A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -376,7 +376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,14 +444,6 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -550,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -630,7 +622,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,9 +1159,9 @@
         <v>59</v>
       </c>
       <c r="B2" s="8">
-        <v>10700265</v>
-      </c>
-      <c r="C2" s="32" t="s">
+        <v>10700464</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>111</v>
       </c>
       <c r="D2" s="9" t="s">
@@ -1199,7 +1190,7 @@
       </c>
       <c r="L2" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>61</v>
@@ -1236,11 +1227,11 @@
       </c>
       <c r="X2" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
-        <v>45913</v>
+        <v>45934</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>76</v>
@@ -1359,9 +1350,9 @@
         <v>101</v>
       </c>
       <c r="B3" s="8">
-        <v>10700266</v>
-      </c>
-      <c r="C3" s="32" t="s">
+        <v>10700465</v>
+      </c>
+      <c r="C3" s="31" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -1390,7 +1381,7 @@
       </c>
       <c r="L3" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>61</v>
@@ -1427,11 +1418,11 @@
       </c>
       <c r="X3" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45913</v>
+        <v>45934</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>76</v>
@@ -1561,6 +1552,6 @@
     <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId5"/>
 </worksheet>
 </file>